--- a/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_los_lagos.xlsx
+++ b/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_los_lagos.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>205.7692307692308</v>
+        <v>205.7692307692307</v>
       </c>
       <c r="C4">
         <v>13.7870083959346</v>
@@ -451,7 +451,7 @@
         <v>15.53575341465196</v>
       </c>
       <c r="D5">
-        <v>58.95113578263093</v>
+        <v>58.95113578263092</v>
       </c>
       <c r="E5">
         <v>25.51311080271712</v>
@@ -486,7 +486,7 @@
         <v>153.7434895833333</v>
       </c>
       <c r="C7">
-        <v>15.90144417412909</v>
+        <v>15.9014441741291</v>
       </c>
       <c r="D7">
         <v>59.65112065841917</v>
@@ -527,10 +527,10 @@
         <v>14.09283708704224</v>
       </c>
       <c r="D9">
-        <v>59.17916243503196</v>
+        <v>59.17916243503197</v>
       </c>
       <c r="E9">
-        <v>26.7280004779258</v>
+        <v>26.72800047792581</v>
       </c>
     </row>
     <row r="10">
@@ -584,7 +584,7 @@
         <v>14.41753653444676</v>
       </c>
       <c r="D12">
-        <v>62.8455114822547</v>
+        <v>62.84551148225469</v>
       </c>
       <c r="E12">
         <v>22.73695198329854</v>
@@ -600,7 +600,7 @@
         <v>130.0114111829593</v>
       </c>
       <c r="C13">
-        <v>15.09878244888583</v>
+        <v>15.09878244888582</v>
       </c>
       <c r="D13">
         <v>65.27107741787273</v>
@@ -682,7 +682,7 @@
         <v>62.31221423905944</v>
       </c>
       <c r="E17">
-        <v>22.66492488569562</v>
+        <v>22.66492488569563</v>
       </c>
     </row>
     <row r="18">
@@ -720,7 +720,7 @@
         <v>61.70029129355918</v>
       </c>
       <c r="E19">
-        <v>24.80310713129787</v>
+        <v>24.80310713129788</v>
       </c>
     </row>
     <row r="20">
@@ -736,7 +736,7 @@
         <v>13.18953323903819</v>
       </c>
       <c r="D20">
-        <v>62.70627062706271</v>
+        <v>62.7062706270627</v>
       </c>
       <c r="E20">
         <v>24.10419613389911</v>
@@ -755,7 +755,7 @@
         <v>15.64876452668397</v>
       </c>
       <c r="D21">
-        <v>63.49768701342661</v>
+        <v>63.4976870134266</v>
       </c>
       <c r="E21">
         <v>20.85354845988943</v>
@@ -774,7 +774,7 @@
         <v>15.54368259622044</v>
       </c>
       <c r="D22">
-        <v>60.56198674186208</v>
+        <v>60.56198674186207</v>
       </c>
       <c r="E22">
         <v>23.89433066191748</v>
@@ -809,7 +809,7 @@
         <v>169.6941176470588</v>
       </c>
       <c r="C24">
-        <v>14.01345291479821</v>
+        <v>14.0134529147982</v>
       </c>
       <c r="D24">
         <v>62.20654180954893</v>
@@ -831,7 +831,7 @@
         <v>14.52093079773984</v>
       </c>
       <c r="D25">
-        <v>59.71808736861292</v>
+        <v>59.71808736861291</v>
       </c>
       <c r="E25">
         <v>25.76098183364724</v>
@@ -866,7 +866,7 @@
         <v>192.033426183844</v>
       </c>
       <c r="C27">
-        <v>13.53899532357822</v>
+        <v>13.53899532357821</v>
       </c>
       <c r="D27">
         <v>60.46160808568411</v>
@@ -907,10 +907,10 @@
         <v>17.41122565864834</v>
       </c>
       <c r="D29">
-        <v>61.71248568155784</v>
+        <v>61.71248568155785</v>
       </c>
       <c r="E29">
-        <v>20.87628865979381</v>
+        <v>20.87628865979382</v>
       </c>
     </row>
     <row r="30">
@@ -942,7 +942,7 @@
         <v>166.9444444444445</v>
       </c>
       <c r="C31">
-        <v>14.4173007609131</v>
+        <v>14.41730076091309</v>
       </c>
       <c r="D31">
         <v>61.51381657989587</v>
